--- a/dist/id_list_result.xlsx
+++ b/dist/id_list_result.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14.5" customWidth="1" style="2" min="1" max="1"/>
@@ -457,7 +457,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>실패: 이미 사용된 쿠폰입니다.</t>
+          <t>존재하지 않는 쿠폰번호 입니다. 다시 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>존재하지 않는 쿠폰번호 입니다. 다시 확인해 주세요.</t>
         </is>
       </c>
     </row>
@@ -472,7 +477,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>실패: 이미 사용된 쿠폰입니다.</t>
+          <t>존재하지 않는 쿠폰번호 입니다. 다시 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>존재하지 않는 쿠폰번호 입니다. 다시 확인해 주세요.</t>
         </is>
       </c>
     </row>
@@ -487,8 +497,12 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>성공: 쿠폰 사용이 완료 되었습니다.
-앱에 접속하여 우편함을 확인해주세요!</t>
+          <t>존재하지 않는 쿠폰번호 입니다. 다시 확인해 주세요.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>존재하지 않는 쿠폰번호 입니다. 다시 확인해 주세요.</t>
         </is>
       </c>
     </row>
